--- a/templates/if-something-happened-to-me-information-plan/information-plan.xlsx
+++ b/templates/if-something-happened-to-me-information-plan/information-plan.xlsx
@@ -8,26 +8,26 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handoff Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Loops" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Household Guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Things in Progress" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recurring Responsibilities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Authority &amp; Access" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access &amp; Documents" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Test" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Handoff Map'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Open Loops'!$A$4:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Household Guide'!$A$4:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Things in Progress'!$A$4:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recurring Responsibilities'!$A$4:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Authority &amp; Access'!$A$4:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Access &amp; Documents'!$A$4:$E$14</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,8 +115,79 @@
       <color rgb="00C65911"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF17324D"/>
+    </font>
+    <font>
+      <color rgb="FF666666"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF17324D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFC65911"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF008000"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -141,6 +212,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17324D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -214,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -287,6 +378,65 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,112 +816,113 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>If Something Happened to Me Information Plan</t>
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>If I'm Unavailable: Household Information Plan</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>A continuity handoff map for the days and weeks when you cannot explain how the household works.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Help someone you trust find important information and keep household responsibilities moving while you are unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>A small map that helps someone you trust understand the household, find the real records, see open situations, and keep important responsibilities from being missed.</t>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Write down who to contact, where to find important records, what is in progress and what needs to happen next.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>What this is not</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Not an estate plan, password vault, emergency checklist, or duplicate archive of every important document.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Five questions</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Taken together, the plan answers: Who matters?  What exists?  Where does the real information live?  What is happening now?  What needs to keep happening?</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Authority rule</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Point to the governing document, system, institution, or professional. Writing a person's name here does not itself give them legal authority.</t>
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Permission to act</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Listing someone here does not give them legal permission to act for you. Note where the relevant document is kept or which institution or professional to contact.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Security rule</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Never put passwords, PINs, recovery codes, encryption keys, banking credentials, security answers, or other secrets in this workbook. Even without secrets, the completed plan can be sensitive; keep and share it appropriately.</t>
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Keep secrets out</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Do not write passwords, PINs, recovery codes or security answers here. A completed plan may still contain sensitive information. Keep it secure and share it only with people who need it.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Keep it maintainable</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Write each detail once. Use the Handoff Map as an index; keep open situations, recurring responsibilities, formal authorities, and protected access in their natural sections.</t>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Use the Household Guide as an index. Put unfinished tasks in Things in Progress, regular duties in Recurring Responsibilities, and account arrangements in Access &amp; Documents. Keep original records where they belong.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Different from emergency checklist</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>The Family Emergency Document Checklist covers the first minutes and hours. This plan covers the days and weeks after that: context, open loops, recurring duties, and handoff.</t>
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Different from the emergency checklist</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>The Family Emergency Document Checklist covers urgent contacts and information. This plan covers household responsibilities over the following days and weeks.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Start small</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Begin with two or three people to contact, three to five household areas another person could not reconstruct, and anything open or due in the next two weeks.</t>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Start with a few people to contact, household tasks only you know about, and anything due in the next two weeks.</t>
         </is>
       </c>
       <c r="C11" s="19" t="n"/>
@@ -779,40 +930,43 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="20" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Plan owner(s)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>Prepared by</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="n"/>
     </row>
     <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Last reviewed</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="35" t="n"/>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Where the current plan is kept</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
+      <c r="B15" s="35" t="n"/>
     </row>
     <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Who knows this plan exists</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-    </row>
+      <c r="B16" s="35" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>People to Contact First</t>
         </is>
@@ -824,9 +978,9 @@
       <c r="F19" s="20" t="n"/>
     </row>
     <row r="20" ht="35" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Add only the few people someone should contact first. This is contact information, not a grant of authority.</t>
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Add the few people someone should contact first. Their contact details do not give them permission to act on your behalf.</t>
         </is>
       </c>
       <c r="B20" s="19" t="n"/>
@@ -836,31 +990,31 @@
       <c r="F20" s="20" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="37" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>Person / role</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Why they matter</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>Best current contact information</t>
         </is>
       </c>
       <c r="D22" s="20" t="n"/>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>What they already know</t>
         </is>
@@ -868,36 +1022,36 @@
       <c r="F22" s="20" t="n"/>
     </row>
     <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="24" t="inlineStr"/>
-      <c r="B23" s="24" t="inlineStr"/>
-      <c r="C23" s="24" t="inlineStr"/>
+      <c r="A23" s="39" t="inlineStr"/>
+      <c r="B23" s="39" t="inlineStr"/>
+      <c r="C23" s="39" t="inlineStr"/>
       <c r="D23" s="20" t="n"/>
-      <c r="E23" s="24" t="inlineStr"/>
+      <c r="E23" s="39" t="inlineStr"/>
       <c r="F23" s="20" t="n"/>
     </row>
     <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="24" t="inlineStr"/>
-      <c r="B24" s="24" t="inlineStr"/>
-      <c r="C24" s="24" t="inlineStr"/>
+      <c r="A24" s="39" t="inlineStr"/>
+      <c r="B24" s="39" t="inlineStr"/>
+      <c r="C24" s="39" t="inlineStr"/>
       <c r="D24" s="20" t="n"/>
-      <c r="E24" s="24" t="inlineStr"/>
+      <c r="E24" s="39" t="inlineStr"/>
       <c r="F24" s="20" t="n"/>
     </row>
     <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="24" t="inlineStr"/>
-      <c r="B25" s="24" t="inlineStr"/>
-      <c r="C25" s="24" t="inlineStr"/>
+      <c r="A25" s="39" t="inlineStr"/>
+      <c r="B25" s="39" t="inlineStr"/>
+      <c r="C25" s="39" t="inlineStr"/>
       <c r="D25" s="20" t="n"/>
-      <c r="E25" s="24" t="inlineStr"/>
+      <c r="E25" s="39" t="inlineStr"/>
       <c r="F25" s="20" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="n"/>
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
+      <c r="A26" s="37" t="n"/>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -949,9 +1103,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>Household Handoff Map</t>
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>Household Guide</t>
         </is>
       </c>
       <c r="B1" s="19" t="n"/>
@@ -959,136 +1113,137 @@
       <c r="D1" s="20" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Use this as the index. Do not repeat open-loop or recurring details here; those have their own sheets.</t>
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>Use this sheet to show where things are. Put unfinished tasks and regular duties on their separate sheets.</t>
         </is>
       </c>
       <c r="B2" s="19" t="n"/>
       <c r="C2" s="19" t="n"/>
       <c r="D2" s="20" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>What exists / what matters</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>Who matters</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>Where the real information lives</t>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>What needs attention</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>Who to contact</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>Where to find the information</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>Home / property</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr"/>
-      <c r="C5" s="24" t="inlineStr"/>
-      <c r="D5" s="24" t="inlineStr"/>
+      <c r="B5" s="39" t="inlineStr"/>
+      <c r="C5" s="39" t="inlineStr"/>
+      <c r="D5" s="39" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Insurance / claims</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr"/>
-      <c r="C6" s="24" t="inlineStr"/>
-      <c r="D6" s="24" t="inlineStr"/>
+      <c r="B6" s="39" t="inlineStr"/>
+      <c r="C6" s="39" t="inlineStr"/>
+      <c r="D6" s="39" t="inlineStr"/>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>Money / accounts / bills</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr"/>
-      <c r="C7" s="24" t="inlineStr"/>
-      <c r="D7" s="24" t="inlineStr"/>
+      <c r="B7" s="39" t="inlineStr"/>
+      <c r="C7" s="39" t="inlineStr"/>
+      <c r="D7" s="39" t="inlineStr"/>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Health / care</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr"/>
-      <c r="C8" s="24" t="inlineStr"/>
-      <c r="D8" s="24" t="inlineStr"/>
+      <c r="B8" s="39" t="inlineStr"/>
+      <c r="C8" s="39" t="inlineStr"/>
+      <c r="D8" s="39" t="inlineStr"/>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Identity / legal</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr"/>
-      <c r="D9" s="24" t="inlineStr"/>
+      <c r="B9" s="39" t="inlineStr"/>
+      <c r="C9" s="39" t="inlineStr"/>
+      <c r="D9" s="39" t="inlineStr"/>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Children / dependants</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr"/>
-      <c r="C10" s="24" t="inlineStr"/>
-      <c r="D10" s="24" t="inlineStr"/>
+      <c r="B10" s="39" t="inlineStr"/>
+      <c r="C10" s="39" t="inlineStr"/>
+      <c r="D10" s="39" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Pets</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr"/>
-      <c r="C11" s="24" t="inlineStr"/>
-      <c r="D11" s="24" t="inlineStr"/>
+      <c r="B11" s="39" t="inlineStr"/>
+      <c r="C11" s="39" t="inlineStr"/>
+      <c r="D11" s="39" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Vehicles / equipment</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr"/>
-      <c r="C12" s="24" t="inlineStr"/>
-      <c r="D12" s="24" t="inlineStr"/>
+      <c r="B12" s="39" t="inlineStr"/>
+      <c r="C12" s="39" t="inlineStr"/>
+      <c r="D12" s="39" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Digital services / devices</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr"/>
-      <c r="C13" s="24" t="inlineStr"/>
-      <c r="D13" s="24" t="inlineStr"/>
+      <c r="B13" s="39" t="inlineStr"/>
+      <c r="C13" s="39" t="inlineStr"/>
+      <c r="D13" s="39" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr"/>
-      <c r="C14" s="24" t="inlineStr"/>
-      <c r="D14" s="24" t="inlineStr"/>
+      <c r="B14" s="39" t="inlineStr"/>
+      <c r="C14" s="39" t="inlineStr"/>
+      <c r="D14" s="39" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:D14"/>
@@ -1119,154 +1274,155 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Open Loops</t>
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Things in Progress</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Capture situations that can vanish if they live only in your head, inbox, texts, or scattered paperwork.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Record unfinished tasks or situations someone else may need to follow up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Current context</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Next expected step</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>What is happening now</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>What happens next</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Who is involved</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Next check / deadline</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Where supporting information lives</t>
+      <c r="F4" s="42" t="inlineStr">
+        <is>
+          <t>Where to find the details</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Example: water-damage claim</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Insurer approved part of claim; contractor estimate still outstanding.</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Follow up when estimate arrives; send to adjuster.</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Insurer / adjuster / contractor</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>Check next week</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="43" t="inlineStr">
         <is>
           <t>Claims folder + current email thread</t>
         </is>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
+      <c r="A7" s="44" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="A8" s="44" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
+      <c r="A9" s="44" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
+      <c r="A11" s="44" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
+      <c r="A12" s="44" t="n"/>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="44" t="n"/>
     </row>
     <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
+      <c r="A13" s="44" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
     </row>
     <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F14"/>
@@ -1296,149 +1452,150 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Recurring Responsibilities</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Only include responsibilities someone may genuinely need to keep from being missed while you are unavailable.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>List the regular tasks someone needs to keep up while you are unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Responsibility</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>How often / next due</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Who or provider matters</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Where the real information lives</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>Who to contact</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>Where to find the details</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>What another person needs to know</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Example: prescription renewal</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Monthly / next refill date</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Pharmacy / prescribing clinic</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Medication record / pharmacy account</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Refill cannot be missed; do not change medical instructions here.</t>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>Follow the existing prescription and the pharmacy's instructions. Note the refill date here.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
+      <c r="A7" s="44" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
+      <c r="A8" s="44" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
+      <c r="A9" s="44" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
+      <c r="A11" s="44" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
+      <c r="A12" s="44" t="n"/>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
+      <c r="A13" s="44" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
+      <c r="A15" s="44" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
+      <c r="A16" s="44" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E16"/>
@@ -1468,118 +1625,119 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Authority &amp; Access</t>
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Access &amp; Important Documents</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Point to where authority or protected access is managed. Record arrangements, not secrets; use this sheet as pointers, not replacements.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Note how a trusted person can find existing access arrangements and important documents. Do not put passwords or recovery codes here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Service / device / information area</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Where access or recovery is managed</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>What arrangement is set up</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>Where to find access instructions</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>What is already arranged</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Who knows it exists</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Last checked</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Example: password manager</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Provider account settings / protected recovery documentation</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>Account settings and the secure recovery instructions</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Emergency access configured, if applicable</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Trusted person knows the arrangement exists</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr"/>
+      <c r="E5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
+      <c r="A7" s="44" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
+      <c r="A8" s="44" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
+      <c r="A9" s="44" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
+      <c r="A11" s="44" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>Do not store here:</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="45" t="inlineStr">
         <is>
           <t>Passwords, PINs, recovery codes, encryption keys, banking credentials, security answers, or other secrets.</t>
         </is>
@@ -1589,23 +1747,23 @@
       <c r="E12" s="20" t="n"/>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="17" t="inlineStr"/>
-      <c r="B13" s="17" t="inlineStr"/>
-      <c r="C13" s="17" t="inlineStr"/>
-      <c r="D13" s="17" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
+      <c r="A13" s="33" t="inlineStr"/>
+      <c r="B13" s="33" t="inlineStr"/>
+      <c r="C13" s="33" t="inlineStr"/>
+      <c r="D13" s="33" t="inlineStr"/>
+      <c r="E13" s="33" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="17" t="inlineStr"/>
-      <c r="B14" s="17" t="inlineStr"/>
-      <c r="C14" s="17" t="inlineStr"/>
-      <c r="D14" s="17" t="inlineStr"/>
-      <c r="E14" s="17" t="inlineStr"/>
+      <c r="A14" s="33" t="inlineStr"/>
+      <c r="B14" s="33" t="inlineStr"/>
+      <c r="C14" s="33" t="inlineStr"/>
+      <c r="D14" s="33" t="inlineStr"/>
+      <c r="E14" s="33" t="inlineStr"/>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Governing Documents &amp; Professional Contacts</t>
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>Important Documents &amp; Contacts</t>
         </is>
       </c>
       <c r="B15" s="19" t="n"/>
@@ -1614,9 +1772,9 @@
       <c r="E15" s="20" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>This section is a pointer only. The document, institution, account mechanism, or formal process remains the source to rely on.</t>
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Record where the current document is kept and who to contact. This list does not replace the document or change anyone's legal permissions.</t>
         </is>
       </c>
       <c r="B16" s="19" t="n"/>
@@ -1625,82 +1783,82 @@
       <c r="E16" s="20" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr"/>
-      <c r="B17" s="17" t="inlineStr"/>
-      <c r="C17" s="17" t="inlineStr"/>
-      <c r="D17" s="17" t="inlineStr"/>
-      <c r="E17" s="17" t="inlineStr"/>
+      <c r="A17" s="33" t="inlineStr"/>
+      <c r="B17" s="33" t="inlineStr"/>
+      <c r="C17" s="33" t="inlineStr"/>
+      <c r="D17" s="33" t="inlineStr"/>
+      <c r="E17" s="33" t="inlineStr"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Document / arrangement</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>Where the current version lives</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>Where the current copy is kept</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>Professional / institution</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>Who should know it exists</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>Last checked</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>Will / estate documents, if applicable</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr"/>
-      <c r="C19" s="24" t="inlineStr"/>
-      <c r="D19" s="24" t="inlineStr"/>
-      <c r="E19" s="24" t="inlineStr"/>
+      <c r="B19" s="39" t="inlineStr"/>
+      <c r="C19" s="39" t="inlineStr"/>
+      <c r="D19" s="39" t="inlineStr"/>
+      <c r="E19" s="39" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Power of attorney / personal directive / similar, if applicable</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr"/>
-      <c r="C20" s="24" t="inlineStr"/>
-      <c r="D20" s="24" t="inlineStr"/>
-      <c r="E20" s="24" t="inlineStr"/>
+      <c r="B20" s="39" t="inlineStr"/>
+      <c r="C20" s="39" t="inlineStr"/>
+      <c r="D20" s="39" t="inlineStr"/>
+      <c r="E20" s="39" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Beneficiary / account arrangements, if applicable</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr"/>
-      <c r="C21" s="24" t="inlineStr"/>
-      <c r="D21" s="24" t="inlineStr"/>
-      <c r="E21" s="24" t="inlineStr"/>
+      <c r="B21" s="39" t="inlineStr"/>
+      <c r="C21" s="39" t="inlineStr"/>
+      <c r="D21" s="39" t="inlineStr"/>
+      <c r="E21" s="39" t="inlineStr"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr"/>
-      <c r="C22" s="24" t="inlineStr"/>
-      <c r="D22" s="24" t="inlineStr"/>
-      <c r="E22" s="24" t="inlineStr"/>
+      <c r="B22" s="39" t="inlineStr"/>
+      <c r="C22" s="39" t="inlineStr"/>
+      <c r="D22" s="39" t="inlineStr"/>
+      <c r="E22" s="39" t="inlineStr"/>
     </row>
     <row r="23" ht="34" customHeight="1"/>
     <row r="24" ht="48" customHeight="1"/>
@@ -1738,225 +1896,230 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Review &amp; Handoff Test</t>
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Try the Plan Together</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The plan is useful only if another appropriate person can use it without you explaining it.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Ask the person who may use this plan to try it without you explaining each step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Handoff test</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Can they do this?</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Ready?</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>What failed / what to fix</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr"/>
-      <c r="E4" s="7" t="inlineStr"/>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>What to improve</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr"/>
+      <c r="E4" s="42" t="inlineStr"/>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>They know who to contact first.</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="9" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="44" t="n"/>
     </row>
     <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>They can find the records and systems that actually govern important areas.</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="9" t="n"/>
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>They can find the important records and accounts.</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n"/>
+      <c r="C6" s="44" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>They can see current open situations that should not be forgotten.</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="9" t="n"/>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>They can see which unfinished tasks need attention.</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="n"/>
+      <c r="C7" s="44" t="n"/>
     </row>
     <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>They can identify recurring responsibilities that cannot be missed.</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="9" t="n"/>
+      <c r="B8" s="46" t="n"/>
+      <c r="C8" s="44" t="n"/>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>They know where protected access or recovery arrangements are managed without needing secrets written here.</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="9" t="n"/>
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>They know where to find existing access or recovery arrangements. No passwords are written in this plan.</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n"/>
+      <c r="C9" s="44" t="n"/>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>They can distinguish ordinary contacts from authority created by a formal document or account mechanism.</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="9" t="n"/>
-    </row>
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>They understand that being listed as a contact does not give them legal permission to act.</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="44" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Review when the handoff changes</t>
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>Review the plan when things change</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Move or major household/property change</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Marriage, separation, birth, death, or new dependant</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Major account, insurance, or property change</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>New or changed will, power of attorney, personal directive, beneficiary designation, or other governing arrangement</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>An important legal document or account arrangement changes</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Health, care, caregiver, or provider change</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Change in trusted people or who should know the plan exists</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>A major open loop starts or closes</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>An important task or situation starts or ends</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Periodic check for quiet changes in recurring responsibilities, open loops, or access arrangements</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>Check occasionally for changes in bills, unfinished tasks, contacts or access arrangements</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Sources &amp; limits</t>
+      <c r="A24" s="47" t="inlineStr">
+        <is>
+          <t>Sources and limits | Version 0.1.1 | 17 September 2026</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>This is a continuity and organization template, not legal, estate-planning, medical, financial, tax, insurance, privacy, security, or emergency-response advice.</t>
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>This is an information organizer, not a substitute for professional advice or official emergency instructions.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Writing a person's name in this plan does not itself appoint them, change ownership, or create legal authority. Use the governing document/process in your jurisdiction.</t>
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Listing a person does not appoint them, change ownership or give them legal permission to act. Follow the current document and the institution's instructions.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="48" t="inlineStr">
         <is>
           <t>Government of Canada household emergency-planning context: https://www.canada.ca/en/services/policing/emergencies/preparedness/get-prepared/make-plan.html</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="48" t="inlineStr">
         <is>
           <t>Emergency plan form: https://www.canada.ca/en/services/policing/emergencies/preparedness/get-prepared/make-plan/emergency-plan-form.html</t>
         </is>

--- a/templates/if-something-happened-to-me-information-plan/information-plan.xlsx
+++ b/templates/if-something-happened-to-me-information-plan/information-plan.xlsx
@@ -8,26 +8,26 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Household Guide" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Things in Progress" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recurring Responsibilities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access &amp; Documents" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Test" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Household overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Things in progress" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regular responsibilities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access and documents" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Try the plan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Household Guide'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Things in Progress'!$A$4:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recurring Responsibilities'!$A$4:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Access &amp; Documents'!$A$4:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Household overview'!$A$4:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Things in progress'!$A$4:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Regular responsibilities'!$A$4:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Access and documents'!$A$4:$E$14</definedName>
   </definedNames>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,79 +115,8 @@
       <color rgb="00C65911"/>
       <sz val="10"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="FF666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF17324D"/>
-    </font>
-    <font>
-      <color rgb="FF666666"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="FF17324D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="FF666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="FF666666"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="FFC65911"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="FF008000"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -212,26 +141,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF17324D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -305,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -378,65 +287,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -816,113 +666,112 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>If I'm Unavailable: Household Information Plan</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Help someone you trust find important information and keep household responsibilities moving while you are unavailable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Help someone you trust keep things going when you cannot answer questions for a while.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>Write down who to contact, where to find important records, what is in progress and what needs to happen next.</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Write down who to contact, where to find important information, what is in progress and what needs attention.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>What this is not</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Not an estate plan, password vault, emergency checklist, or duplicate archive of every important document.</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>This is a guide to the information, not an estate plan, a password store or a copy of every document.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>Five questions</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>Taken together, the plan answers: Who matters?  What exists?  Where does the real information live?  What is happening now?  What needs to keep happening?</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>What to include</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Who should they contact? What should they know about? Where can they find it? What is in progress? What needs to keep happening?</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>Permission to act</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>Listing someone here does not give them legal permission to act for you. Note where the relevant document is kept or which institution or professional to contact.</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Legal permission</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Listing someone here does not give them legal permission to act for you. Point them to the relevant document, institution or professional.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>Keep secrets out</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>Do not write passwords, PINs, recovery codes or security answers here. A completed plan may still contain sensitive information. Keep it secure and share it only with people who need it.</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Keep private details safe</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Do not enter passwords, PINs, recovery codes or security answers. Even without those details, this plan may be sensitive. Share it only with the people who should see it.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>Keep it maintainable</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>Use the Household Guide as an index. Put unfinished tasks in Things in Progress, regular duties in Recurring Responsibilities, and account arrangements in Access &amp; Documents. Keep original records where they belong.</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Keep it easy to update</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Use Household overview to point to the details. Record unfinished tasks, regular responsibilities and access arrangements on their own sheets.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>Different from the emergency checklist</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>The Family Emergency Document Checklist covers urgent contacts and information. This plan covers household responsibilities over the following days and weeks.</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>How this differs from the emergency checklist</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>The Family Emergency Document Checklist helps with the first minutes and hours. This plan helps someone manage the days and weeks after that.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Start small</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>Start with a few people to contact, household tasks only you know about, and anything due in the next two weeks.</t>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Start with a few people to contact, the household information someone else would not know, and anything due in the next two weeks.</t>
         </is>
       </c>
       <c r="C11" s="19" t="n"/>
@@ -930,43 +779,40 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="20" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n"/>
+      <c r="B13" s="6" t="n"/>
     </row>
     <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Last reviewed</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n"/>
+      <c r="B14" s="6" t="n"/>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Where the current plan is kept</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n"/>
+      <c r="B15" s="6" t="n"/>
     </row>
     <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Who knows this plan exists</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+      <c r="B16" s="6" t="n"/>
+    </row>
     <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>People to Contact First</t>
         </is>
@@ -978,9 +824,9 @@
       <c r="F19" s="20" t="n"/>
     </row>
     <row r="20" ht="35" customHeight="1">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>Add the few people someone should contact first. Their contact details do not give them permission to act on your behalf.</t>
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>List the first few people to contact and how they can help. Their names here do not give them legal authority.</t>
         </is>
       </c>
       <c r="B20" s="19" t="n"/>
@@ -990,31 +836,31 @@
       <c r="F20" s="20" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="n"/>
-      <c r="B21" s="37" t="n"/>
-      <c r="C21" s="37" t="n"/>
-      <c r="D21" s="37" t="n"/>
-      <c r="E21" s="37" t="n"/>
-      <c r="F21" s="37" t="n"/>
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Person / role</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Why they matter</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Best current contact information</t>
         </is>
       </c>
       <c r="D22" s="20" t="n"/>
-      <c r="E22" s="38" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>What they already know</t>
         </is>
@@ -1022,36 +868,36 @@
       <c r="F22" s="20" t="n"/>
     </row>
     <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="39" t="inlineStr"/>
-      <c r="B23" s="39" t="inlineStr"/>
-      <c r="C23" s="39" t="inlineStr"/>
+      <c r="A23" s="24" t="inlineStr"/>
+      <c r="B23" s="24" t="inlineStr"/>
+      <c r="C23" s="24" t="inlineStr"/>
       <c r="D23" s="20" t="n"/>
-      <c r="E23" s="39" t="inlineStr"/>
+      <c r="E23" s="24" t="inlineStr"/>
       <c r="F23" s="20" t="n"/>
     </row>
     <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="39" t="inlineStr"/>
-      <c r="B24" s="39" t="inlineStr"/>
-      <c r="C24" s="39" t="inlineStr"/>
+      <c r="A24" s="24" t="inlineStr"/>
+      <c r="B24" s="24" t="inlineStr"/>
+      <c r="C24" s="24" t="inlineStr"/>
       <c r="D24" s="20" t="n"/>
-      <c r="E24" s="39" t="inlineStr"/>
+      <c r="E24" s="24" t="inlineStr"/>
       <c r="F24" s="20" t="n"/>
     </row>
     <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="39" t="inlineStr"/>
-      <c r="B25" s="39" t="inlineStr"/>
-      <c r="C25" s="39" t="inlineStr"/>
+      <c r="A25" s="24" t="inlineStr"/>
+      <c r="B25" s="24" t="inlineStr"/>
+      <c r="C25" s="24" t="inlineStr"/>
       <c r="D25" s="20" t="n"/>
-      <c r="E25" s="39" t="inlineStr"/>
+      <c r="E25" s="24" t="inlineStr"/>
       <c r="F25" s="20" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="n"/>
-      <c r="B26" s="37" t="n"/>
-      <c r="C26" s="37" t="n"/>
-      <c r="D26" s="37" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="37" t="n"/>
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1103,9 +949,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="40" t="inlineStr">
-        <is>
-          <t>Household Guide</t>
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Household overview</t>
         </is>
       </c>
       <c r="B1" s="19" t="n"/>
@@ -1113,137 +959,136 @@
       <c r="D1" s="20" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
-        <is>
-          <t>Use this sheet to show where things are. Put unfinished tasks and regular duties on their separate sheets.</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Use this as your index. Put unfinished tasks and regular responsibilities on their own sheets.</t>
         </is>
       </c>
       <c r="B2" s="19" t="n"/>
       <c r="C2" s="19" t="n"/>
       <c r="D2" s="20" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
-        <is>
-          <t>What needs attention</t>
-        </is>
-      </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>What someone needs to know</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Who to contact</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Where to find the information</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Home / property</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr"/>
-      <c r="C5" s="39" t="inlineStr"/>
-      <c r="D5" s="39" t="inlineStr"/>
+      <c r="B5" s="24" t="inlineStr"/>
+      <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Insurance / claims</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr"/>
-      <c r="C6" s="39" t="inlineStr"/>
-      <c r="D6" s="39" t="inlineStr"/>
+      <c r="B6" s="24" t="inlineStr"/>
+      <c r="C6" s="24" t="inlineStr"/>
+      <c r="D6" s="24" t="inlineStr"/>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Money / accounts / bills</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr"/>
-      <c r="C7" s="39" t="inlineStr"/>
-      <c r="D7" s="39" t="inlineStr"/>
+      <c r="B7" s="24" t="inlineStr"/>
+      <c r="C7" s="24" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr"/>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Health / care</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr"/>
-      <c r="C8" s="39" t="inlineStr"/>
-      <c r="D8" s="39" t="inlineStr"/>
+      <c r="B8" s="24" t="inlineStr"/>
+      <c r="C8" s="24" t="inlineStr"/>
+      <c r="D8" s="24" t="inlineStr"/>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Identity / legal</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr"/>
-      <c r="C9" s="39" t="inlineStr"/>
-      <c r="D9" s="39" t="inlineStr"/>
+      <c r="B9" s="24" t="inlineStr"/>
+      <c r="C9" s="24" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr"/>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Children / dependants</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr"/>
-      <c r="C10" s="39" t="inlineStr"/>
-      <c r="D10" s="39" t="inlineStr"/>
+      <c r="B10" s="24" t="inlineStr"/>
+      <c r="C10" s="24" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Pets</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr"/>
-      <c r="C11" s="39" t="inlineStr"/>
-      <c r="D11" s="39" t="inlineStr"/>
+      <c r="B11" s="24" t="inlineStr"/>
+      <c r="C11" s="24" t="inlineStr"/>
+      <c r="D11" s="24" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Vehicles / equipment</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr"/>
-      <c r="C12" s="39" t="inlineStr"/>
-      <c r="D12" s="39" t="inlineStr"/>
+      <c r="B12" s="24" t="inlineStr"/>
+      <c r="C12" s="24" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Digital services / devices</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr"/>
-      <c r="C13" s="39" t="inlineStr"/>
-      <c r="D13" s="39" t="inlineStr"/>
+      <c r="B13" s="24" t="inlineStr"/>
+      <c r="C13" s="24" t="inlineStr"/>
+      <c r="D13" s="24" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr"/>
-      <c r="C14" s="39" t="inlineStr"/>
-      <c r="D14" s="39" t="inlineStr"/>
+      <c r="B14" s="24" t="inlineStr"/>
+      <c r="C14" s="24" t="inlineStr"/>
+      <c r="D14" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:D14"/>
@@ -1274,155 +1119,154 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Things in Progress</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Things in progress</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Record unfinished tasks or situations someone else may need to follow up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Record unfinished tasks and ongoing situations that someone else could easily miss.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>What is happening now</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>What happens next</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Next step</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Who is involved</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
-        <is>
-          <t>Next check / deadline</t>
-        </is>
-      </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Date to check or deadline</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Where to find the details</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Example: water-damage claim</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Fictional example: water-damage claim</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Insurer approved part of claim; contractor estimate still outstanding.</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Follow up when estimate arrives; send to adjuster.</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Insurer / adjuster / contractor</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Check next week</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Claims folder + current email thread</t>
         </is>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="44" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="44" t="n"/>
-      <c r="F6" s="44" t="n"/>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="44" t="n"/>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
-      <c r="F7" s="44" t="n"/>
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="44" t="n"/>
-      <c r="B8" s="44" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="44" t="n"/>
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="44" t="n"/>
-      <c r="B9" s="44" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="44" t="n"/>
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="44" t="n"/>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="44" t="n"/>
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="44" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="44" t="n"/>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
     </row>
     <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="44" t="n"/>
-      <c r="B13" s="44" t="n"/>
-      <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
     </row>
     <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="44" t="n"/>
-      <c r="B14" s="44" t="n"/>
-      <c r="C14" s="44" t="n"/>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="44" t="n"/>
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F14"/>
@@ -1452,150 +1296,149 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Recurring Responsibilities</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Regular responsibilities</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>List the regular tasks someone needs to keep up while you are unavailable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Include the things someone needs to keep doing while you are unavailable.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Responsibility</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>How often / next due</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>Who to contact</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Person or service to contact</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Where to find the details</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>What another person needs to know</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Example: prescription renewal</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Fictional example: prescription renewal</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Monthly / next refill date</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Pharmacy / prescribing clinic</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Medication record / pharmacy account</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
-        <is>
-          <t>Follow the existing prescription and the pharmacy's instructions. Note the refill date here.</t>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Refill cannot be missed; do not change medical instructions here.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="44" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="44" t="n"/>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="44" t="n"/>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="44" t="n"/>
-      <c r="B8" s="44" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="44" t="n"/>
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="44" t="n"/>
-      <c r="B9" s="44" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="44" t="n"/>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="44" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="44" t="n"/>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="44" t="n"/>
-      <c r="B13" s="44" t="n"/>
-      <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="44" t="n"/>
-      <c r="B14" s="44" t="n"/>
-      <c r="C14" s="44" t="n"/>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="44" t="n"/>
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="44" t="n"/>
-      <c r="B15" s="44" t="n"/>
-      <c r="C15" s="44" t="n"/>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="44" t="n"/>
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="44" t="n"/>
-      <c r="B16" s="44" t="n"/>
-      <c r="C16" s="44" t="n"/>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="44" t="n"/>
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E16"/>
@@ -1625,119 +1468,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Access &amp; Important Documents</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Access and important documents</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Note how a trusted person can find existing access arrangements and important documents. Do not put passwords or recovery codes here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Explain where access arrangements are managed and where important documents are kept. Do not enter passwords or recovery codes.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>Service / device / information area</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>Where to find access instructions</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>What is already arranged</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Account, device or information</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Where to arrange access or recovery</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>What has been arranged</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Who knows it exists</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Last checked</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Example: password manager</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Fictional example: password manager</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Account settings and the secure recovery instructions</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Emergency access configured, if applicable</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Trusted person knows the arrangement exists</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="44" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="44" t="n"/>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="44" t="n"/>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="44" t="n"/>
-      <c r="B8" s="44" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="44" t="n"/>
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="44" t="n"/>
-      <c r="B9" s="44" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="44" t="n"/>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="44" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Do not store here:</t>
         </is>
       </c>
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Passwords, PINs, recovery codes, encryption keys, banking credentials, security answers, or other secrets.</t>
         </is>
@@ -1747,23 +1589,23 @@
       <c r="E12" s="20" t="n"/>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="33" t="inlineStr"/>
-      <c r="B13" s="33" t="inlineStr"/>
-      <c r="C13" s="33" t="inlineStr"/>
-      <c r="D13" s="33" t="inlineStr"/>
-      <c r="E13" s="33" t="inlineStr"/>
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr"/>
+      <c r="E13" s="17" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="33" t="inlineStr"/>
-      <c r="B14" s="33" t="inlineStr"/>
-      <c r="C14" s="33" t="inlineStr"/>
-      <c r="D14" s="33" t="inlineStr"/>
-      <c r="E14" s="33" t="inlineStr"/>
+      <c r="A14" s="17" t="inlineStr"/>
+      <c r="B14" s="17" t="inlineStr"/>
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr"/>
+      <c r="E14" s="17" t="inlineStr"/>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t>Important Documents &amp; Contacts</t>
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Important documents and professional contacts</t>
         </is>
       </c>
       <c r="B15" s="19" t="n"/>
@@ -1772,9 +1614,9 @@
       <c r="E15" s="20" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>Record where the current document is kept and who to contact. This list does not replace the document or change anyone's legal permissions.</t>
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Write down where the current document is kept and who can explain it. This plan does not replace the document or the process for using it.</t>
         </is>
       </c>
       <c r="B16" s="19" t="n"/>
@@ -1783,82 +1625,82 @@
       <c r="E16" s="20" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr"/>
-      <c r="B17" s="33" t="inlineStr"/>
-      <c r="C17" s="33" t="inlineStr"/>
-      <c r="D17" s="33" t="inlineStr"/>
-      <c r="E17" s="33" t="inlineStr"/>
+      <c r="A17" s="17" t="inlineStr"/>
+      <c r="B17" s="17" t="inlineStr"/>
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="17" t="inlineStr"/>
+      <c r="E17" s="17" t="inlineStr"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Document / arrangement</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
-        <is>
-          <t>Where the current copy is kept</t>
-        </is>
-      </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Where the current version is kept</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Professional / institution</t>
         </is>
       </c>
-      <c r="D18" s="38" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>Who should know it exists</t>
         </is>
       </c>
-      <c r="E18" s="38" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>Last checked</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Will / estate documents, if applicable</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr"/>
-      <c r="C19" s="39" t="inlineStr"/>
-      <c r="D19" s="39" t="inlineStr"/>
-      <c r="E19" s="39" t="inlineStr"/>
+      <c r="B19" s="24" t="inlineStr"/>
+      <c r="C19" s="24" t="inlineStr"/>
+      <c r="D19" s="24" t="inlineStr"/>
+      <c r="E19" s="24" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Power of attorney / personal directive / similar, if applicable</t>
         </is>
       </c>
-      <c r="B20" s="39" t="inlineStr"/>
-      <c r="C20" s="39" t="inlineStr"/>
-      <c r="D20" s="39" t="inlineStr"/>
-      <c r="E20" s="39" t="inlineStr"/>
+      <c r="B20" s="24" t="inlineStr"/>
+      <c r="C20" s="24" t="inlineStr"/>
+      <c r="D20" s="24" t="inlineStr"/>
+      <c r="E20" s="24" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Beneficiary / account arrangements, if applicable</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr"/>
-      <c r="C21" s="39" t="inlineStr"/>
-      <c r="D21" s="39" t="inlineStr"/>
-      <c r="E21" s="39" t="inlineStr"/>
+      <c r="B21" s="24" t="inlineStr"/>
+      <c r="C21" s="24" t="inlineStr"/>
+      <c r="D21" s="24" t="inlineStr"/>
+      <c r="E21" s="24" t="inlineStr"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="41" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B22" s="39" t="inlineStr"/>
-      <c r="C22" s="39" t="inlineStr"/>
-      <c r="D22" s="39" t="inlineStr"/>
-      <c r="E22" s="39" t="inlineStr"/>
+      <c r="B22" s="24" t="inlineStr"/>
+      <c r="C22" s="24" t="inlineStr"/>
+      <c r="D22" s="24" t="inlineStr"/>
+      <c r="E22" s="24" t="inlineStr"/>
     </row>
     <row r="23" ht="34" customHeight="1"/>
     <row r="24" ht="48" customHeight="1"/>
@@ -1896,230 +1738,225 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Try the Plan Together</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Try the plan with someone you trust</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Ask the person who may use this plan to try it without you explaining each step.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ask the person who may use this plan to try it without you explaining where everything is.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>Can they do this?</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>What to try</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Ready?</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>What to improve</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr"/>
-      <c r="E4" s="42" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>What failed / what to fix</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>They know who to contact first.</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n"/>
-      <c r="C5" s="44" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="9" t="n"/>
     </row>
     <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>They can find the important records and accounts.</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="44" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="9" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>They can see which unfinished tasks need attention.</t>
-        </is>
-      </c>
-      <c r="B7" s="46" t="n"/>
-      <c r="C7" s="44" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>They can see unfinished tasks and ongoing situations.</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="9" t="n"/>
     </row>
     <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>They can identify recurring responsibilities that cannot be missed.</t>
-        </is>
-      </c>
-      <c r="B8" s="46" t="n"/>
-      <c r="C8" s="44" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>They can identify regular responsibilities that need attention.</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="9" t="n"/>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>They know where to find existing access or recovery arrangements. No passwords are written in this plan.</t>
-        </is>
-      </c>
-      <c r="B9" s="46" t="n"/>
-      <c r="C9" s="44" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>They know where to find access or recovery instructions without secrets written in this plan.</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="9" t="n"/>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>They understand that being listed as a contact does not give them legal permission to act.</t>
-        </is>
-      </c>
-      <c r="B10" s="46" t="n"/>
-      <c r="C10" s="44" t="n"/>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>They know that being a contact is different from having legal or account permission.</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="9" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>Review the plan when things change</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>When to update the plan</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Move or major household/property change</t>
         </is>
       </c>
-      <c r="E14" s="44" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Marriage, separation, birth, death, or new dependant</t>
         </is>
       </c>
-      <c r="E15" s="44" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Major account, insurance, or property change</t>
         </is>
       </c>
-      <c r="E16" s="44" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>An important legal document or account arrangement changes</t>
-        </is>
-      </c>
-      <c r="E17" s="44" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A will, power of attorney, personal directive, beneficiary or other legal arrangement changes</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>Health, care, caregiver, or provider change</t>
-        </is>
-      </c>
-      <c r="E18" s="44" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Health, care or caregiver arrangements change</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Change in trusted people or who should know the plan exists</t>
         </is>
       </c>
-      <c r="E19" s="44" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>An important task or situation starts or ends</t>
-        </is>
-      </c>
-      <c r="E20" s="44" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>An important task or ongoing situation starts or ends</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>Check occasionally for changes in bills, unfinished tasks, contacts or access arrangements</t>
-        </is>
-      </c>
-      <c r="E21" s="44" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>A regular review finds changes to responsibilities, unfinished tasks or access arrangements</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Reviewed?</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24">
-      <c r="A24" s="47" t="inlineStr">
-        <is>
-          <t>Sources and limits | Version 0.1.1 | 17 September 2026</t>
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Sources and limits</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>This is an information organizer, not a substitute for professional advice or official emergency instructions.</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>This plan helps organize household information. Use the relevant official documents and professional advice for legal, medical, financial or emergency decisions.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>Listing a person does not appoint them, change ownership or give them legal permission to act. Follow the current document and the institution's instructions.</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Listing someone here does not appoint them or change ownership. Check the document, account rules or local process that gives them permission to act.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Government of Canada household emergency-planning context: https://www.canada.ca/en/services/policing/emergencies/preparedness/get-prepared/make-plan.html</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Emergency plan form: https://www.canada.ca/en/services/policing/emergencies/preparedness/get-prepared/make-plan/emergency-plan-form.html</t>
         </is>

--- a/templates/if-something-happened-to-me-information-plan/information-plan.xlsx
+++ b/templates/if-something-happened-to-me-information-plan/information-plan.xlsx
@@ -8,19 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handoff Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Loops" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recurring Responsibilities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Authority &amp; Access" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Test" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Household overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Things in progress" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regular responsibilities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access and documents" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Try the plan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Handoff Map'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Open Loops'!$A$4:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recurring Responsibilities'!$A$4:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Authority &amp; Access'!$A$4:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Household overview'!$A$4:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Things in progress'!$A$4:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Regular responsibilities'!$A$4:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Access and documents'!$A$4:$E$14</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -668,14 +668,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>If Something Happened to Me Information Plan</t>
+          <t>If I'm Unavailable: Household Information Plan</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A continuity handoff map for the days and weeks when you cannot explain how the household works.</t>
+          <t>Help someone you trust keep things going when you cannot answer questions for a while.</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>A small map that helps someone you trust understand the household, find the real records, see open situations, and keep important responsibilities from being missed.</t>
+          <t>Write down who to contact, where to find important information, what is in progress and what needs attention.</t>
         </is>
       </c>
     </row>
@@ -699,67 +699,67 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Not an estate plan, password vault, emergency checklist, or duplicate archive of every important document.</t>
+          <t>This is a guide to the information, not an estate plan, a password store or a copy of every document.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Five questions</t>
+          <t>What to include</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Taken together, the plan answers: Who matters?  What exists?  Where does the real information live?  What is happening now?  What needs to keep happening?</t>
+          <t>Who should they contact? What should they know about? Where can they find it? What is in progress? What needs to keep happening?</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Authority rule</t>
+          <t>Legal permission</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Point to the governing document, system, institution, or professional. Writing a person's name here does not itself give them legal authority.</t>
+          <t>Listing someone here does not give them legal permission to act for you. Point them to the relevant document, institution or professional.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Security rule</t>
+          <t>Keep private details safe</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Never put passwords, PINs, recovery codes, encryption keys, banking credentials, security answers, or other secrets in this workbook. Even without secrets, the completed plan can be sensitive; keep and share it appropriately.</t>
+          <t>Do not enter passwords, PINs, recovery codes or security answers. Even without those details, this plan may be sensitive. Share it only with the people who should see it.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Keep it maintainable</t>
+          <t>Keep it easy to update</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Write each detail once. Use the Handoff Map as an index; keep open situations, recurring responsibilities, formal authorities, and protected access in their natural sections.</t>
+          <t>Use Household overview to point to the details. Record unfinished tasks, regular responsibilities and access arrangements on their own sheets.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Different from emergency checklist</t>
+          <t>How this differs from the emergency checklist</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>The Family Emergency Document Checklist covers the first minutes and hours. This plan covers the days and weeks after that: context, open loops, recurring duties, and handoff.</t>
+          <t>The Family Emergency Document Checklist helps with the first minutes and hours. This plan helps someone manage the days and weeks after that.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Begin with two or three people to contact, three to five household areas another person could not reconstruct, and anything open or due in the next two weeks.</t>
+          <t>Start with a few people to contact, the household information someone else would not know, and anything due in the next two weeks.</t>
         </is>
       </c>
       <c r="C11" s="19" t="n"/>
@@ -782,7 +782,7 @@
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Plan owner(s)</t>
+          <t>Prepared by</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
@@ -826,7 +826,7 @@
     <row r="20" ht="35" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Add only the few people someone should contact first. This is contact information, not a grant of authority.</t>
+          <t>List the first few people to contact and how they can help. Their names here do not give them legal authority.</t>
         </is>
       </c>
       <c r="B20" s="19" t="n"/>
@@ -951,7 +951,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>Household Handoff Map</t>
+          <t>Household overview</t>
         </is>
       </c>
       <c r="B1" s="19" t="n"/>
@@ -961,7 +961,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Use this as the index. Do not repeat open-loop or recurring details here; those have their own sheets.</t>
+          <t>Use this as your index. Put unfinished tasks and regular responsibilities on their own sheets.</t>
         </is>
       </c>
       <c r="B2" s="19" t="n"/>
@@ -976,17 +976,17 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>What exists / what matters</t>
+          <t>What someone needs to know</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>Who matters</t>
+          <t>Who to contact</t>
         </is>
       </c>
       <c r="D4" s="22" t="inlineStr">
         <is>
-          <t>Where the real information lives</t>
+          <t>Where to find the information</t>
         </is>
       </c>
     </row>
@@ -1121,14 +1121,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Loops</t>
+          <t>Things in progress</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Capture situations that can vanish if they live only in your head, inbox, texts, or scattered paperwork.</t>
+          <t>Record unfinished tasks and ongoing situations that someone else could easily miss.</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Current context</t>
+          <t>What is happening now</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Next expected step</t>
+          <t>Next step</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Next check / deadline</t>
+          <t>Date to check or deadline</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Where supporting information lives</t>
+          <t>Where to find the details</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Example: water-damage claim</t>
+          <t>Fictional example: water-damage claim</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1298,14 +1298,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Recurring Responsibilities</t>
+          <t>Regular responsibilities</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Only include responsibilities someone may genuinely need to keep from being missed while you are unavailable.</t>
+          <t>Include the things someone needs to keep doing while you are unavailable.</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Who or provider matters</t>
+          <t>Person or service to contact</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Where the real information lives</t>
+          <t>Where to find the details</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Example: prescription renewal</t>
+          <t>Fictional example: prescription renewal</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1470,31 +1470,31 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Authority &amp; Access</t>
+          <t>Access and important documents</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Point to where authority or protected access is managed. Record arrangements, not secrets; use this sheet as pointers, not replacements.</t>
+          <t>Explain where access arrangements are managed and where important documents are kept. Do not enter passwords or recovery codes.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Service / device / information area</t>
+          <t>Account, device or information</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Where access or recovery is managed</t>
+          <t>Where to arrange access or recovery</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>What arrangement is set up</t>
+          <t>What has been arranged</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Example: password manager</t>
+          <t>Fictional example: password manager</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Provider account settings / protected recovery documentation</t>
+          <t>Account settings and the secure recovery instructions</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Governing Documents &amp; Professional Contacts</t>
+          <t>Important documents and professional contacts</t>
         </is>
       </c>
       <c r="B15" s="19" t="n"/>
@@ -1616,7 +1616,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>This section is a pointer only. The document, institution, account mechanism, or formal process remains the source to rely on.</t>
+          <t>Write down where the current document is kept and who can explain it. This plan does not replace the document or the process for using it.</t>
         </is>
       </c>
       <c r="B16" s="19" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Where the current version lives</t>
+          <t>Where the current version is kept</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -1740,21 +1740,21 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Review &amp; Handoff Test</t>
+          <t>Try the plan with someone you trust</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The plan is useful only if another appropriate person can use it without you explaining it.</t>
+          <t>Ask the person who may use this plan to try it without you explaining where everything is.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Handoff test</t>
+          <t>What to try</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>They can find the records and systems that actually govern important areas.</t>
+          <t>They can find the important records and accounts.</t>
         </is>
       </c>
       <c r="B6" s="13" t="n"/>
@@ -1791,7 +1791,7 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>They can see current open situations that should not be forgotten.</t>
+          <t>They can see unfinished tasks and ongoing situations.</t>
         </is>
       </c>
       <c r="B7" s="13" t="n"/>
@@ -1800,7 +1800,7 @@
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>They can identify recurring responsibilities that cannot be missed.</t>
+          <t>They can identify regular responsibilities that need attention.</t>
         </is>
       </c>
       <c r="B8" s="13" t="n"/>
@@ -1809,7 +1809,7 @@
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>They know where protected access or recovery arrangements are managed without needing secrets written here.</t>
+          <t>They know where to find access or recovery instructions without secrets written in this plan.</t>
         </is>
       </c>
       <c r="B9" s="13" t="n"/>
@@ -1818,7 +1818,7 @@
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>They can distinguish ordinary contacts from authority created by a formal document or account mechanism.</t>
+          <t>They know that being a contact is different from having legal or account permission.</t>
         </is>
       </c>
       <c r="B10" s="13" t="n"/>
@@ -1827,7 +1827,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Review when the handoff changes</t>
+          <t>When to update the plan</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>New or changed will, power of attorney, personal directive, beneficiary designation, or other governing arrangement</t>
+          <t>A will, power of attorney, personal directive, beneficiary or other legal arrangement changes</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Health, care, caregiver, or provider change</t>
+          <t>Health, care or caregiver arrangements change</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A major open loop starts or closes</t>
+          <t>An important task or ongoing situation starts or ends</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1918,7 +1918,7 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Periodic check for quiet changes in recurring responsibilities, open loops, or access arrangements</t>
+          <t>A regular review finds changes to responsibilities, unfinished tasks or access arrangements</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1930,21 +1930,21 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Sources &amp; limits</t>
+          <t>Sources and limits</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>This is a continuity and organization template, not legal, estate-planning, medical, financial, tax, insurance, privacy, security, or emergency-response advice.</t>
+          <t>This plan helps organize household information. Use the relevant official documents and professional advice for legal, medical, financial or emergency decisions.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Writing a person's name in this plan does not itself appoint them, change ownership, or create legal authority. Use the governing document/process in your jurisdiction.</t>
+          <t>Listing someone here does not appoint them or change ownership. Check the document, account rules or local process that gives them permission to act.</t>
         </is>
       </c>
     </row>
